--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488028_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488028_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1595</v>
+        <v>1.3925</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4587</v>
+        <v>1.5232</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2992</v>
+        <v>-0.1307</v>
       </c>
       <c r="G2" t="n">
         <v>3.1184</v>
@@ -610,13 +610,13 @@
         <v>3.1716</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7328</v>
+        <v>-1.0342</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7733</v>
+        <v>-0.1622</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0405</v>
+        <v>-0.872</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8811</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8561</v>
+        <v>1.3579</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3296</v>
+        <v>1.5334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5265</v>
+        <v>-0.1755</v>
       </c>
       <c r="G3" t="n">
         <v>-1.2248</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>0.288</v>
+        <v>-0.2102</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.433</v>
+        <v>-0.2293</v>
       </c>
       <c r="U3" t="n">
-        <v>0.721</v>
+        <v>0.019</v>
       </c>
       <c r="V3" t="n">
         <v>1.2071</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>E. TRUJILLO MARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5528</v>
+        <v>-0.2874</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8461</v>
+        <v>0.9181</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2933</v>
+        <v>-1.2055</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0568</v>
+        <v>1.2923</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3834</v>
+        <v>0.973</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6734</v>
+        <v>0.3193</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.659</v>
+        <v>4.2541</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0202</v>
+        <v>1.6828</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6791</v>
+        <v>2.5714</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3979</v>
+        <v>-2.9618</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4036</v>
+        <v>-0.7098</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0057</v>
+        <v>-2.252</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>-4.1627</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-6.9378</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1982</v>
+        <v>2.7751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3057</v>
+        <v>-1.305</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1872</v>
+        <v>-0.2861</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4929</v>
+        <v>-1.0189</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>3.8879</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.8879</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0299</v>
+        <v>-0.5456</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4916</v>
+        <v>-0.6424</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5383</v>
+        <v>0.0968</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.786</v>
+        <v>-1.0568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2343</v>
+        <v>-0.3834</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0203</v>
+        <v>-0.6734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1006</v>
+        <v>-0.659</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8082</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7076</v>
+        <v>-0.6791</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8866</v>
+        <v>-0.3979</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5739</v>
+        <v>-0.4036</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3126</v>
+        <v>0.0057</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3787</v>
+        <v>0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3698</v>
+        <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6820000000000001</v>
+        <v>0.3129</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1324</v>
+        <v>0.0165</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8144</v>
+        <v>0.2964</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. TRUJILLO MARIN</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2709</v>
+        <v>-1.1775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1031</v>
+        <v>-0.6953</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.374</v>
+        <v>-0.4821</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2923</v>
+        <v>-1.786</v>
       </c>
       <c r="H7" t="n">
-        <v>0.973</v>
+        <v>0.2343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3193</v>
+        <v>-2.0203</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2541</v>
+        <v>0.1006</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6828</v>
+        <v>0.8082</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5714</v>
+        <v>-0.7076</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9618</v>
+        <v>-1.8866</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7098</v>
+        <v>-0.5739</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.252</v>
+        <v>-1.3126</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.1627</v>
+        <v>2.3787</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.9378</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7751</v>
+        <v>3.3698</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.2884</v>
+        <v>-0.8296</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1011</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1873</v>
+        <v>-0.7582</v>
       </c>
       <c r="V7" t="n">
-        <v>3.8879</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8879</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3591</v>
+        <v>-1.2011</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4005</v>
+        <v>-1.2986</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0414</v>
+        <v>0.0975</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3342</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.025</v>
+        <v>0.1331</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1313</v>
+        <v>-2.5309</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9274</v>
+        <v>-3.1035</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0587</v>
+        <v>0.5726</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.007</v>
+        <v>-2.6186</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1599</v>
+        <v>-2.5458</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1529</v>
+        <v>-0.0728</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2908</v>
+        <v>-2.3195</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2908</v>
+        <v>-2.3597</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.2991</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8691</v>
+        <v>-0.1861</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1529</v>
+        <v>-0.113</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8231000000000001</v>
+        <v>-1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6851</v>
+        <v>-0.0595</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.862</v>
+        <v>-1.1106</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1692</v>
+        <v>-2.992</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7979</v>
+        <v>0.0106</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6287</v>
+        <v>-3.0025</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6186</v>
+        <v>-2.007</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5458</v>
+        <v>-2.1599</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0728</v>
+        <v>0.1529</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3195</v>
+        <v>-1.2908</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3597</v>
+        <v>-1.2908</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2991</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1861</v>
+        <v>-0.8691</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.113</v>
+        <v>0.1529</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8083</v>
+        <v>-0.0376</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2461</v>
+        <v>0.7682</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0544</v>
+        <v>-0.8058</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2666</v>
+        <v>-1.7403</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.2734</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4962</v>
+        <v>-3.2082</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.276</v>
+        <v>-3.0723</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2201</v>
+        <v>-0.1359</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6465</v>
@@ -1312,13 +1312,13 @@
         <v>2.7751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3938</v>
+        <v>-1.1058</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5578</v>
+        <v>-0.354</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.836</v>
+        <v>-0.7518</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5415</v>
+        <v>-4.7618</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3691</v>
+        <v>-4.7579</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1724</v>
+        <v>-0.004</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5719</v>
@@ -1390,13 +1390,13 @@
         <v>1.5858</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8992</v>
+        <v>-1.1195</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1232</v>
+        <v>-0.5119</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7761</v>
+        <v>-0.6076</v>
       </c>
       <c r="V12" t="n">
         <v>-0.674</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6658</v>
+        <v>-5.0545</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2118</v>
+        <v>-1.6006</v>
       </c>
       <c r="F13" t="n">
         <v>-3.4539</v>
@@ -1468,10 +1468,10 @@
         <v>0.9911</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6482</v>
+        <v>-1.037</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.3247</v>
       </c>
       <c r="U13" t="n">
         <v>-0.7122000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.630800000000001</v>
+        <v>-8.8231</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.9253</v>
+        <v>-6.3141</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7055</v>
+        <v>-2.509</v>
       </c>
       <c r="G14" t="n">
         <v>-4.0021</v>
@@ -1546,13 +1546,13 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2146</v>
+        <v>-1.4068</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0497</v>
+        <v>-0.4385</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1648</v>
+        <v>-0.9683</v>
       </c>
       <c r="V14" t="n">
         <v>-3.0178</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-27.5292</v>
+        <v>-27.529</v>
       </c>
       <c r="E15" t="n">
-        <v>-17.1968</v>
+        <v>-17.1967</v>
       </c>
       <c r="F15" t="n">
         <v>-10.3322</v>
@@ -1603,7 +1603,7 @@
         <v>-0.2353999999999996</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8213999999999999</v>
+        <v>-0.8213999999999995</v>
       </c>
       <c r="M15" t="n">
         <v>-13.6843</v>
@@ -1624,19 +1624,19 @@
         <v>21.8045</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.809899999999999</v>
+        <v>-8.809699999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6135</v>
+        <v>-1.6134</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.196400000000001</v>
+        <v>-7.1964</v>
       </c>
       <c r="V15" t="n">
         <v>-4.9694</v>
       </c>
       <c r="W15" t="n">
-        <v>6.287000000000002</v>
+        <v>6.287000000000001</v>
       </c>
       <c r="X15" t="n">
         <v>-11.2563</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>13.5748</v>
+        <v>13.2398</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6827</v>
+        <v>11.0714</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8921</v>
+        <v>2.1684</v>
       </c>
       <c r="G16" t="n">
         <v>6.1854</v>
@@ -1702,13 +1702,13 @@
         <v>2.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1824</v>
+        <v>1.8474</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1036</v>
+        <v>1.4924</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0788</v>
+        <v>0.355</v>
       </c>
       <c r="V16" t="n">
         <v>3.6213</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.4367</v>
+        <v>5.0334</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6562</v>
+        <v>4.8928</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7805</v>
+        <v>0.1406</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2103</v>
+        <v>2.8768</v>
       </c>
       <c r="H17" t="n">
-        <v>3.1836</v>
+        <v>0.3189</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0267</v>
+        <v>2.5579</v>
       </c>
       <c r="J17" t="n">
-        <v>3.026</v>
+        <v>2.9174</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4238</v>
+        <v>0.9086</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3979</v>
+        <v>2.0089</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1843</v>
+        <v>-0.0406</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2403</v>
+        <v>-0.5896</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4246</v>
+        <v>0.549</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7596</v>
+        <v>0.5708</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3459</v>
+        <v>0.7682</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4136</v>
+        <v>-0.1974</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7997</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.1633</v>
+        <v>4.6997</v>
       </c>
       <c r="E18" t="n">
-        <v>4.9947</v>
+        <v>2.4338</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1687</v>
+        <v>2.2659</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8768</v>
+        <v>3.2103</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3189</v>
+        <v>3.1836</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5579</v>
+        <v>0.0267</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9174</v>
+        <v>3.026</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9086</v>
+        <v>3.4238</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0089</v>
+        <v>-0.3979</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0406</v>
+        <v>0.1843</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5896</v>
+        <v>-0.2403</v>
       </c>
       <c r="O18" t="n">
-        <v>0.549</v>
+        <v>0.4246</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7007</v>
+        <v>2.0226</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8701</v>
+        <v>1.1235</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1694</v>
+        <v>0.8991</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2933</v>
+        <v>2.3304</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4234</v>
+        <v>-1.544</v>
       </c>
       <c r="F19" t="n">
-        <v>4.7168</v>
+        <v>3.8744</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5637</v>
@@ -1936,13 +1936,13 @@
         <v>2.3787</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7955</v>
+        <v>1.8326</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2284</v>
+        <v>1.1078</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5672</v>
+        <v>0.7248</v>
       </c>
       <c r="V19" t="n">
         <v>0.674</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.208</v>
+        <v>1.9702</v>
       </c>
       <c r="E21" t="n">
-        <v>1.208</v>
+        <v>-1.6505</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.6207</v>
       </c>
       <c r="G21" t="n">
-        <v>1.208</v>
+        <v>0.1165</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.2199</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6027</v>
+        <v>-0.1034</v>
       </c>
       <c r="J21" t="n">
-        <v>1.208</v>
+        <v>-0.1356</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.4168</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6027</v>
+        <v>0.2812</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.2521</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.6367</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3847</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.2591</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.4673</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2053</v>
+        <v>1.6118</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2053</v>
+        <v>-0.7885</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2.4003</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2053</v>
+        <v>-1.388</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-3.3396</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2053</v>
+        <v>1.9516</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2053</v>
+        <v>-1.6365</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-2.8976</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2053</v>
+        <v>1.2611</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.2485</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-0.442</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.6905</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.5769</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.4735</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.3654</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.1081</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9574</v>
+        <v>1.208</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3636</v>
+        <v>1.208</v>
       </c>
       <c r="F23" t="n">
-        <v>3.321</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1165</v>
+        <v>1.208</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2199</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1034</v>
+        <v>0.6027</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1356</v>
+        <v>1.208</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4168</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2812</v>
+        <v>0.6027</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2521</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.6367</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3847</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2462</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2458</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.492</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7851</v>
+        <v>1.2053</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3997</v>
+        <v>1.2053</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1848</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.388</v>
+        <v>1.2053</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3396</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9516</v>
+        <v>1.2053</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.6365</v>
+        <v>1.2053</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.8976</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2611</v>
+        <v>1.2053</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2485</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.442</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6905</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3532</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2458</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1074</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9405</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2648</v>
+        <v>0.4661</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0844</v>
+        <v>-2.9714</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3492</v>
+        <v>3.4375</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1102</v>
+        <v>1.817</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1102</v>
+        <v>-0.2801</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.097</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0404</v>
+        <v>0.9728</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0404</v>
+        <v>-0.1678</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.1405</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0699</v>
+        <v>0.8442</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0699</v>
+        <v>-0.1123</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.9565</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3964</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3964</v>
+        <v>2.5769</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2419</v>
+        <v>0.0367</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1248</v>
+        <v>0.0203</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1171</v>
+        <v>0.0164</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2341</v>
+        <v>0.4261</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1213</v>
+        <v>-0.7139</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8873</v>
+        <v>1.14</v>
       </c>
       <c r="G26" t="n">
         <v>-2.8249</v>
@@ -2482,13 +2482,13 @@
         <v>0.9911</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5135999999999999</v>
+        <v>1.1737</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4406</v>
+        <v>0.8481</v>
       </c>
       <c r="U26" t="n">
-        <v>0.073</v>
+        <v>0.3257</v>
       </c>
       <c r="V26" t="n">
         <v>2.0772</v>
@@ -2503,7 +2503,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,58 +2515,58 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2666</v>
+        <v>0.2929</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.1751</v>
+        <v>-0.0844</v>
       </c>
       <c r="F27" t="n">
-        <v>2.9086</v>
+        <v>0.3773</v>
       </c>
       <c r="G27" t="n">
-        <v>1.817</v>
+        <v>0.1102</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2801</v>
+        <v>0.1102</v>
       </c>
       <c r="I27" t="n">
-        <v>2.097</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9728</v>
+        <v>0.0404</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1678</v>
+        <v>0.0404</v>
       </c>
       <c r="L27" t="n">
-        <v>1.1405</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8442</v>
+        <v>0.0699</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1123</v>
+        <v>0.0699</v>
       </c>
       <c r="O27" t="n">
-        <v>0.9565</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.5769</v>
+        <v>0.3964</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.696</v>
+        <v>-0.2138</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1834</v>
+        <v>-0.1248</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.089</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2593,64 +2593,64 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.3188</v>
+        <v>-0.2591</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4609</v>
+        <v>-1.0891</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.8579</v>
+        <v>0.83</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2662</v>
+        <v>1.7192</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4129</v>
+        <v>0.2593</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6791</v>
+        <v>1.4599</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3361</v>
+        <v>1.2108</v>
       </c>
       <c r="K28" t="n">
-        <v>0.343</v>
+        <v>0.034</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.6791</v>
+        <v>1.1768</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0699</v>
+        <v>0.5084</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0699</v>
+        <v>0.2253</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3964</v>
+        <v>-3.568</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.2419</v>
+        <v>0.3827</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1248</v>
+        <v>0.2415</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1171</v>
+        <v>0.1412</v>
       </c>
       <c r="V28" t="n">
-        <v>-1.2071</v>
+        <v>1.2071</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.4142</v>
       </c>
       <c r="X28" t="n">
         <v>-1.2071</v>
@@ -2659,7 +2659,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2671,64 +2671,64 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.7283</v>
+        <v>-1.2907</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.0059</v>
+        <v>-0.4609</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2776</v>
+        <v>-0.8298</v>
       </c>
       <c r="G29" t="n">
-        <v>1.7192</v>
+        <v>-0.2662</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2593</v>
+        <v>0.4129</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4599</v>
+        <v>-0.6791</v>
       </c>
       <c r="J29" t="n">
-        <v>1.2108</v>
+        <v>-0.3361</v>
       </c>
       <c r="K29" t="n">
-        <v>0.034</v>
+        <v>0.343</v>
       </c>
       <c r="L29" t="n">
-        <v>1.1768</v>
+        <v>-0.6791</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5084</v>
+        <v>0.0699</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2253</v>
+        <v>0.0699</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-3.568</v>
+        <v>0.3964</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4.9556</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.0866</v>
+        <v>-0.2138</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.6753</v>
+        <v>-0.1248</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.4113</v>
+        <v>-0.089</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2071</v>
+        <v>-1.2071</v>
       </c>
       <c r="W29" t="n">
-        <v>2.4142</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>-1.2071</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-4.9252</v>
+        <v>-4.1599</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.4935</v>
+        <v>-3.2897</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4317</v>
+        <v>-0.8702</v>
       </c>
       <c r="G30" t="n">
         <v>0.2221</v>
@@ -2794,13 +2794,13 @@
         <v>1.3876</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2313</v>
+        <v>0.9966</v>
       </c>
       <c r="T30" t="n">
-        <v>0.8077</v>
+        <v>1.0115</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.5764</v>
+        <v>-0.0148</v>
       </c>
       <c r="V30" t="n">
         <v>-1.8107</v>
@@ -2827,19 +2827,19 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>27.52900000000001</v>
+        <v>28.8873</v>
       </c>
       <c r="E31" t="n">
-        <v>10.3324</v>
+        <v>10.3322</v>
       </c>
       <c r="F31" t="n">
-        <v>17.197</v>
+        <v>18.5551</v>
       </c>
       <c r="G31" t="n">
         <v>14.7413</v>
       </c>
       <c r="H31" t="n">
-        <v>4.074600000000001</v>
+        <v>4.0746</v>
       </c>
       <c r="I31" t="n">
         <v>10.6666</v>
@@ -2851,19 +2851,19 @@
         <v>3.8393</v>
       </c>
       <c r="L31" t="n">
-        <v>9.844700000000001</v>
+        <v>9.8447</v>
       </c>
       <c r="M31" t="n">
         <v>1.0572</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2354000000000001</v>
+        <v>0.2354</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8216999999999999</v>
+        <v>0.8217000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.9911000000000003</v>
+        <v>-0.9910999999999994</v>
       </c>
       <c r="Q31" t="n">
         <v>-21.8045</v>
@@ -2872,13 +2872,13 @@
         <v>20.8134</v>
       </c>
       <c r="S31" t="n">
-        <v>8.809700000000001</v>
+        <v>10.1681</v>
       </c>
       <c r="T31" t="n">
         <v>7.196400000000001</v>
       </c>
       <c r="U31" t="n">
-        <v>1.613299999999999</v>
+        <v>2.9719</v>
       </c>
       <c r="V31" t="n">
         <v>4.9692</v>
@@ -2887,7 +2887,7 @@
         <v>11.2563</v>
       </c>
       <c r="X31" t="n">
-        <v>-6.287000000000001</v>
+        <v>-6.286999999999999</v>
       </c>
     </row>
   </sheetData>
